--- a/ops/finanzas/CONTROL_PAGOS_PROVEEDORES_CMC2026.xlsx
+++ b/ops/finanzas/CONTROL_PAGOS_PROVEEDORES_CMC2026.xlsx
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Catering desayuno VIP 800 pax — Presupuesto S03362</t>
+          <t>Catering desayuno VIP 600 pax — Presupuesto S03362</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
@@ -1329,22 +1329,22 @@
         </is>
       </c>
       <c r="F9" s="31" t="n">
-        <v>16696800</v>
+        <v>12522600</v>
       </c>
       <c r="G9" s="31" t="n">
-        <v>3506328</v>
+        <v>2629746</v>
       </c>
       <c r="H9" s="32" t="n">
-        <v>20203128</v>
+        <v>15152346</v>
       </c>
       <c r="I9" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="J9" s="31" t="n">
-        <v>10101564</v>
+        <v>7576173</v>
       </c>
       <c r="K9" s="31" t="n">
-        <v>10101564</v>
+        <v>7576173</v>
       </c>
       <c r="L9" s="34" t="n"/>
       <c r="M9" s="35" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="O9" s="36" t="inlineStr">
         <is>
-          <t>800 pax × $20.871 + IVA. Ejecutiva: Ángeles García Laborde. Cuenta a nombre de Good Events SA, NO Gourmet Connection SA. Anticipo unificado con S03363.</t>
+          <t>CORREGIDO A 600 pax × $20.871 + IVA. El presupuesto S03362 y la invoice 2601021 se emitieron por 800: Ángeles García Laborde no hizo el ajuste. RECLAMAR la reemisión antes de señar. Cuenta a nombre de Good Events SA, NO Gourmet Connection SA.</t>
         </is>
       </c>
     </row>
@@ -1451,25 +1451,25 @@
         </is>
       </c>
       <c r="F11" s="31" t="n">
-        <v>12477450</v>
+        <v>10390350</v>
       </c>
       <c r="G11" s="31" t="n">
-        <v>2620264.5</v>
+        <v>2181973.5</v>
       </c>
       <c r="H11" s="32" t="n">
-        <v>15097714.5</v>
+        <v>12572323.5</v>
       </c>
       <c r="I11" s="33" t="n">
         <v>0.5</v>
       </c>
       <c r="J11" s="31" t="n">
-        <v>15097714.5</v>
+        <v>12572323.5</v>
       </c>
       <c r="K11" s="31" t="n">
-        <v>15097714.5</v>
+        <v>12572323.5</v>
       </c>
       <c r="L11" s="34" t="n">
-        <v>9835.639999999999</v>
+        <v>8190.44</v>
       </c>
       <c r="M11" s="35" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="O11" s="36" t="inlineStr">
         <is>
-          <t>ESTA es la invoice emitida. Base neta total $24.954.900. Saldo 50% pendiente de emitir.</t>
+          <t>ANTICIPO CORREGIDO a 600 desayunos: base neta total $20.780.700. OJO: la invoice 2601021 emitida dice $15.097.714,50 porque está calculada sobre 800 desayunos. Si se paga como está se transfieren $2.525.391 de más (US$1.645). Pedir la reemisión. Saldo 50% pendiente de emitir.</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="B6" s="72" t="inlineStr">
         <is>
-          <t>Catering desayuno VIP 800 pax — Presupuesto S03362</t>
+          <t>Catering desayuno VIP 600 pax — Presupuesto S03362</t>
         </is>
       </c>
       <c r="C6" s="73" t="inlineStr">
@@ -4218,10 +4218,10 @@
         <v/>
       </c>
       <c r="D7" s="100" t="n">
-        <v>31148580.93</v>
+        <v>26097798.93</v>
       </c>
       <c r="E7" s="101" t="n">
-        <v>9835.639999999999</v>
+        <v>8190.44</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
